--- a/data/trans_dic/P36$fruta-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P36$fruta-Provincia-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que desayuna, al menos, fruta o zumo</t>
+          <t>Población que desayuna, al menos, fruta o zumo (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,74; 7,98</t>
+          <t>2,44; 7,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,64; 16,58</t>
+          <t>8,85; 16,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,46; 14,17</t>
+          <t>6,82; 14,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,51; 8,04</t>
+          <t>2,41; 8,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,78; 18,34</t>
+          <t>9,46; 18,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,08; 15,39</t>
+          <t>8,05; 15,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,2; 6,98</t>
+          <t>3,1; 6,76</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,42; 16,16</t>
+          <t>10,32; 16,12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,31; 13,28</t>
+          <t>8,19; 13,43</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,63; 17,05</t>
+          <t>10,58; 16,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,29; 15,67</t>
+          <t>9,35; 15,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,7; 13,27</t>
+          <t>7,72; 13,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,26; 16,88</t>
+          <t>10,93; 16,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,54; 10,46</t>
+          <t>5,65; 10,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,38; 13,95</t>
+          <t>8,23; 14,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,65; 16,16</t>
+          <t>11,67; 16,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,1; 11,95</t>
+          <t>8,19; 12,17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,61; 12,6</t>
+          <t>8,73; 12,78</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,77; 7,84</t>
+          <t>2,52; 7,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,45; 13,18</t>
+          <t>6,16; 13,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,1; 14,13</t>
+          <t>7,26; 13,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,17; 13,8</t>
+          <t>7,12; 13,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11,62; 19,74</t>
+          <t>11,67; 19,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,1; 13,61</t>
+          <t>7,25; 13,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,68; 9,72</t>
+          <t>5,69; 10,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,95; 15,3</t>
+          <t>9,83; 15,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,88; 12,32</t>
+          <t>7,85; 12,46</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,51; 8,49</t>
+          <t>3,56; 8,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,81; 14,43</t>
+          <t>7,76; 14,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,66; 18,92</t>
+          <t>11,26; 19,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,34; 14,86</t>
+          <t>8,66; 14,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,86; 15,99</t>
+          <t>8,87; 15,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,5; 14,37</t>
+          <t>7,69; 14,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,68; 10,94</t>
+          <t>6,67; 10,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,11; 13,81</t>
+          <t>9,05; 13,55</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,56; 15,6</t>
+          <t>10,45; 15,48</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,15; 7,8</t>
+          <t>2,1; 8,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,74; 11,12</t>
+          <t>3,66; 10,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,6; 17,87</t>
+          <t>8,82; 18,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,41; 7,37</t>
+          <t>1,46; 7,09</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,29; 11,64</t>
+          <t>3,94; 11,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,37; 18,39</t>
+          <t>9,31; 18,48</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,32; 6,32</t>
+          <t>2,29; 6,24</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,65; 9,56</t>
+          <t>4,72; 9,57</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10,17; 16,43</t>
+          <t>10,27; 16,89</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,76; 5,94</t>
+          <t>1,71; 6,01</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,71; 14,88</t>
+          <t>7,29; 15,09</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10,19; 19,14</t>
+          <t>9,29; 18,43</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,7; 15,7</t>
+          <t>8,04; 15,67</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10,84; 19,88</t>
+          <t>11,42; 20,04</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,68; 19,25</t>
+          <t>11,06; 19,58</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,34; 9,83</t>
+          <t>5,16; 9,7</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,01; 16,1</t>
+          <t>9,83; 15,88</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11,49; 17,46</t>
+          <t>11,26; 17,32</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,2; 11,05</t>
+          <t>6,45; 10,96</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12,04; 17,92</t>
+          <t>12,12; 18,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14,62; 20,93</t>
+          <t>14,52; 20,75</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,32; 18,12</t>
+          <t>12,19; 18,1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>14,68; 20,43</t>
+          <t>14,47; 20,51</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,13; 21,0</t>
+          <t>15,25; 21,26</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,02; 13,73</t>
+          <t>9,99; 13,68</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>14,02; 18,27</t>
+          <t>13,94; 18,27</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>15,92; 20,13</t>
+          <t>15,77; 20,06</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>8,62; 13,34</t>
+          <t>8,49; 13,17</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>11,05; 15,7</t>
+          <t>10,88; 15,77</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,83; 14,59</t>
+          <t>10,02; 14,55</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6,56; 10,96</t>
+          <t>6,67; 10,8</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,02; 13,82</t>
+          <t>9,02; 13,71</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,51; 16,31</t>
+          <t>11,45; 16,41</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,14; 11,24</t>
+          <t>7,99; 11,06</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>10,28; 13,66</t>
+          <t>10,42; 13,87</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>11,24; 14,67</t>
+          <t>11,26; 14,83</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7,17; 9,19</t>
+          <t>7,11; 9,18</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>10,97; 13,25</t>
+          <t>10,89; 13,2</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11,9; 14,16</t>
+          <t>11,88; 14,31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9,66; 11,82</t>
+          <t>9,54; 11,64</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>11,53; 13,74</t>
+          <t>11,57; 13,81</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,31; 14,69</t>
+          <t>12,17; 14,47</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,72; 10,18</t>
+          <t>8,63; 10,11</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>11,46; 13,09</t>
+          <t>11,44; 13,12</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>12,34; 14,01</t>
+          <t>12,34; 13,99</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que desayuna, al menos, fruta o zumo</t>
+          <t>Población que desayuna, al menos, fruta o zumo (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7442; 21640</t>
+          <t>6615; 20900</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>25471; 48866</t>
+          <t>26088; 48909</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18982; 41633</t>
+          <t>20042; 41416</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6510; 20883</t>
+          <t>6253; 21807</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>28010; 52507</t>
+          <t>27093; 54270</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23329; 44432</t>
+          <t>23241; 45766</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17017; 37087</t>
+          <t>16444; 35910</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>60536; 93879</t>
+          <t>59985; 93657</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>48425; 77358</t>
+          <t>47729; 78242</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>52318; 83885</t>
+          <t>52041; 83111</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>46880; 79062</t>
+          <t>47160; 79300</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38516; 66418</t>
+          <t>38652; 67036</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>56744; 85070</t>
+          <t>55097; 85280</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>28897; 54589</t>
+          <t>29486; 55116</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>43855; 72971</t>
+          <t>43059; 73432</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>115982; 160924</t>
+          <t>116246; 160350</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>83076; 122648</t>
+          <t>84014; 124923</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>88080; 128983</t>
+          <t>89376; 130782</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8821; 25013</t>
+          <t>8022; 24443</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>20840; 42593</t>
+          <t>19902; 42828</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22608; 44998</t>
+          <t>23123; 43524</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24059; 46298</t>
+          <t>23893; 46308</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>39643; 67302</t>
+          <t>39798; 65549</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23867; 45761</t>
+          <t>24373; 45778</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37153; 63613</t>
+          <t>37236; 65412</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>66052; 101621</t>
+          <t>65271; 101326</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>51616; 80683</t>
+          <t>51376; 81625</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12564; 30372</t>
+          <t>12729; 31050</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>29123; 53797</t>
+          <t>28937; 53398</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>43120; 69999</t>
+          <t>41640; 71203</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>30983; 55211</t>
+          <t>32181; 55150</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>34445; 62185</t>
+          <t>34501; 61925</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29062; 55656</t>
+          <t>29783; 54563</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>48714; 79800</t>
+          <t>48616; 78521</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>69406; 105220</t>
+          <t>68925; 103195</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>79991; 118093</t>
+          <t>79124; 117230</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4354; 15793</t>
+          <t>4247; 16415</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7960; 23646</t>
+          <t>7782; 23210</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18166; 37750</t>
+          <t>18639; 38987</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2904; 15236</t>
+          <t>3023; 14652</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>9413; 25557</t>
+          <t>8649; 24872</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20487; 40196</t>
+          <t>20360; 40385</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9473; 25841</t>
+          <t>9370; 25532</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>20093; 41320</t>
+          <t>20410; 41376</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>43714; 70596</t>
+          <t>44120; 72616</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4753; 16074</t>
+          <t>4629; 16278</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>18392; 40761</t>
+          <t>19972; 41343</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>26817; 50360</t>
+          <t>24445; 48484</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>21431; 43659</t>
+          <t>22354; 43571</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>30254; 55456</t>
+          <t>31855; 55900</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>29035; 52343</t>
+          <t>30063; 53237</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>29322; 53972</t>
+          <t>28343; 53225</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>55330; 89053</t>
+          <t>54339; 87814</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>61470; 93417</t>
+          <t>60244; 92677</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>38024; 67714</t>
+          <t>39518; 67188</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>79785; 118796</t>
+          <t>80350; 121374</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>95715; 137059</t>
+          <t>95040; 135836</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>78357; 115289</t>
+          <t>77550; 115143</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>101870; 141782</t>
+          <t>100424; 142306</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>104275; 144729</t>
+          <t>105105; 146545</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>125180; 171506</t>
+          <t>124802; 170872</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>190205; 247872</t>
+          <t>189120; 247827</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>214015; 270579</t>
+          <t>211923; 269548</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>64090; 99188</t>
+          <t>63159; 97932</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>85796; 121841</t>
+          <t>84475; 122445</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>76562; 113619</t>
+          <t>78016; 113280</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>51411; 85876</t>
+          <t>52250; 84597</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>74102; 113550</t>
+          <t>74142; 112661</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>95062; 134715</t>
+          <t>94592; 135598</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>124259; 171709</t>
+          <t>122008; 168955</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>164268; 218315</t>
+          <t>166435; 221576</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>180380; 235475</t>
+          <t>180687; 237986</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>234573; 300452</t>
+          <t>232577; 300228</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>375159; 453293</t>
+          <t>372498; 451700</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>403547; 479964</t>
+          <t>402872; 485161</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>326152; 398925</t>
+          <t>321891; 392999</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>409578; 488101</t>
+          <t>411155; 490463</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>435813; 520047</t>
+          <t>431133; 512593</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>579619; 676510</t>
+          <t>573255; 671909</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>798805; 912944</t>
+          <t>797553; 915117</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>855413; 971375</t>
+          <t>855408; 969735</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P36$fruta-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P36$fruta-Provincia-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,44; 7,71</t>
+          <t>2,72; 7,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,85; 16,59</t>
+          <t>8,87; 17,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,82; 14,1</t>
+          <t>6,49; 13,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,41; 8,39</t>
+          <t>2,52; 8,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,46; 18,96</t>
+          <t>10,04; 19,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,05; 15,85</t>
+          <t>7,83; 15,59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,1; 6,76</t>
+          <t>3,05; 6,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,32; 16,12</t>
+          <t>10,61; 16,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,19; 13,43</t>
+          <t>8,13; 13,4</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,58; 16,89</t>
+          <t>10,56; 17,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,35; 15,72</t>
+          <t>9,52; 15,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,72; 13,4</t>
+          <t>7,78; 13,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,93; 16,92</t>
+          <t>11,25; 17,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,65; 10,56</t>
+          <t>5,59; 10,47</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,23; 14,04</t>
+          <t>8,36; 14,09</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,67; 16,1</t>
+          <t>11,77; 16,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,19; 12,17</t>
+          <t>8,15; 12,17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,73; 12,78</t>
+          <t>8,78; 12,72</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,52; 7,67</t>
+          <t>2,69; 8,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,16; 13,25</t>
+          <t>6,32; 12,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,26; 13,66</t>
+          <t>7,19; 13,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,12; 13,81</t>
+          <t>7,13; 13,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11,67; 19,22</t>
+          <t>11,76; 19,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,25; 13,61</t>
+          <t>6,83; 13,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,69; 10,0</t>
+          <t>5,68; 9,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,83; 15,26</t>
+          <t>9,96; 15,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,85; 12,46</t>
+          <t>8,03; 12,62</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,56; 8,68</t>
+          <t>3,42; 8,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,76; 14,32</t>
+          <t>7,8; 14,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,26; 19,25</t>
+          <t>11,52; 19,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,66; 14,85</t>
+          <t>8,47; 14,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,87; 15,92</t>
+          <t>8,76; 15,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,69; 14,09</t>
+          <t>7,81; 14,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,67; 10,77</t>
+          <t>6,79; 10,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,05; 13,55</t>
+          <t>9,03; 13,9</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,45; 15,48</t>
+          <t>10,44; 15,58</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,1; 8,11</t>
+          <t>2,15; 8,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,66; 10,92</t>
+          <t>3,8; 10,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,82; 18,46</t>
+          <t>8,85; 17,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,46; 7,09</t>
+          <t>1,44; 6,97</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,94; 11,33</t>
+          <t>3,99; 10,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,31; 18,48</t>
+          <t>9,78; 17,95</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,29; 6,24</t>
+          <t>2,36; 6,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,72; 9,57</t>
+          <t>4,74; 9,6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10,27; 16,89</t>
+          <t>10,44; 16,9</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,71; 6,01</t>
+          <t>1,48; 5,8</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,29; 15,09</t>
+          <t>7,17; 14,5</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,29; 18,43</t>
+          <t>9,98; 18,37</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,04; 15,67</t>
+          <t>7,82; 15,43</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11,42; 20,04</t>
+          <t>11,27; 19,97</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11,06; 19,58</t>
+          <t>10,21; 18,89</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,16; 9,7</t>
+          <t>5,52; 9,89</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9,83; 15,88</t>
+          <t>10,37; 15,92</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11,26; 17,32</t>
+          <t>11,27; 17,52</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,45; 10,96</t>
+          <t>6,47; 10,96</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12,12; 18,31</t>
+          <t>12,11; 18,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14,52; 20,75</t>
+          <t>14,54; 20,87</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,19; 18,1</t>
+          <t>12,37; 18,09</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>14,47; 20,51</t>
+          <t>14,49; 20,56</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,25; 21,26</t>
+          <t>15,37; 21,43</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,99; 13,68</t>
+          <t>10,13; 13,6</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>13,94; 18,27</t>
+          <t>14,03; 18,49</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>15,77; 20,06</t>
+          <t>15,83; 20,13</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>8,49; 13,17</t>
+          <t>8,63; 13,24</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10,88; 15,77</t>
+          <t>10,91; 15,89</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10,02; 14,55</t>
+          <t>9,84; 14,81</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6,67; 10,8</t>
+          <t>6,29; 10,5</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,02; 13,71</t>
+          <t>8,85; 13,73</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,45; 16,41</t>
+          <t>11,63; 16,53</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,99; 11,06</t>
+          <t>8,02; 11,23</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>10,42; 13,87</t>
+          <t>10,37; 13,8</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>11,26; 14,83</t>
+          <t>11,38; 14,63</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7,11; 9,18</t>
+          <t>7,12; 9,12</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>10,89; 13,2</t>
+          <t>10,93; 13,17</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11,88; 14,31</t>
+          <t>11,97; 14,21</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9,54; 11,64</t>
+          <t>9,69; 11,89</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>11,57; 13,81</t>
+          <t>11,47; 13,8</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,17; 14,47</t>
+          <t>12,2; 14,48</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,63; 10,11</t>
+          <t>8,66; 10,12</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>11,44; 13,12</t>
+          <t>11,48; 13,15</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>12,34; 13,99</t>
+          <t>12,37; 14,0</t>
         </is>
       </c>
     </row>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6615; 20900</t>
+          <t>7365; 21280</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>26088; 48909</t>
+          <t>26138; 50454</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20042; 41416</t>
+          <t>19058; 40092</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6253; 21807</t>
+          <t>6534; 20834</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>27093; 54270</t>
+          <t>28744; 54741</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23241; 45766</t>
+          <t>22614; 45017</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16444; 35910</t>
+          <t>16193; 36534</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>59985; 93657</t>
+          <t>61626; 96359</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>47729; 78242</t>
+          <t>47336; 78027</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>52041; 83111</t>
+          <t>51963; 83711</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>47160; 79300</t>
+          <t>48041; 78444</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38652; 67036</t>
+          <t>38938; 65484</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>55097; 85280</t>
+          <t>56712; 87194</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>29486; 55116</t>
+          <t>29165; 54633</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>43059; 73432</t>
+          <t>43722; 73695</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>116246; 160350</t>
+          <t>117247; 161092</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>84014; 124923</t>
+          <t>83678; 124878</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>89376; 130782</t>
+          <t>89890; 130139</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8022; 24443</t>
+          <t>8574; 25814</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>19902; 42828</t>
+          <t>20409; 41757</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23123; 43524</t>
+          <t>22912; 43370</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23893; 46308</t>
+          <t>23932; 46138</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>39798; 65549</t>
+          <t>40099; 67496</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24373; 45778</t>
+          <t>22985; 44560</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37236; 65412</t>
+          <t>37178; 63725</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>65271; 101326</t>
+          <t>66178; 100856</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>51376; 81625</t>
+          <t>52590; 82648</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12729; 31050</t>
+          <t>12227; 30691</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>28937; 53398</t>
+          <t>29071; 52858</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>41640; 71203</t>
+          <t>42604; 72337</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>32181; 55150</t>
+          <t>31479; 55165</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>34501; 61925</t>
+          <t>34059; 61819</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29783; 54563</t>
+          <t>30260; 55775</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>48616; 78521</t>
+          <t>49527; 79318</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>68925; 103195</t>
+          <t>68831; 105917</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>79124; 117230</t>
+          <t>79032; 117966</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4247; 16415</t>
+          <t>4362; 16815</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7782; 23210</t>
+          <t>8074; 23236</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18639; 38987</t>
+          <t>18689; 37125</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3023; 14652</t>
+          <t>2969; 14409</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>8649; 24872</t>
+          <t>8765; 24133</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20360; 40385</t>
+          <t>21374; 39235</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9370; 25532</t>
+          <t>9643; 26435</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>20410; 41376</t>
+          <t>20489; 41493</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>44120; 72616</t>
+          <t>44869; 72652</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4629; 16278</t>
+          <t>4021; 15696</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>19972; 41343</t>
+          <t>19653; 39731</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>24445; 48484</t>
+          <t>26262; 48325</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>22354; 43571</t>
+          <t>21737; 42912</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>31855; 55900</t>
+          <t>31439; 55704</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>30063; 53237</t>
+          <t>27758; 51353</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28343; 53225</t>
+          <t>30324; 54298</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>54339; 87814</t>
+          <t>57337; 88027</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>60244; 92677</t>
+          <t>60306; 93735</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>39518; 67188</t>
+          <t>39638; 67178</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>80350; 121374</t>
+          <t>80233; 120318</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>95040; 135836</t>
+          <t>95209; 136652</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>77550; 115143</t>
+          <t>78724; 115119</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>100424; 142306</t>
+          <t>100524; 142645</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>105105; 146545</t>
+          <t>105967; 147721</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>124802; 170872</t>
+          <t>126553; 169928</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>189120; 247827</t>
+          <t>190375; 250810</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>211923; 269548</t>
+          <t>212781; 270497</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>63159; 97932</t>
+          <t>64161; 98450</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>84475; 122445</t>
+          <t>84662; 123351</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>78016; 113280</t>
+          <t>76615; 115334</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>52250; 84597</t>
+          <t>49274; 82295</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>74142; 112661</t>
+          <t>72705; 112804</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>94592; 135598</t>
+          <t>96094; 136539</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>122008; 168955</t>
+          <t>122415; 171544</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>166435; 221576</t>
+          <t>165762; 220574</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>180687; 237986</t>
+          <t>182547; 234811</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>232577; 300228</t>
+          <t>232687; 298110</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>372498; 451700</t>
+          <t>373824; 450597</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>402872; 485161</t>
+          <t>405948; 481800</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>321891; 392999</t>
+          <t>327110; 401198</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>411155; 490463</t>
+          <t>407260; 490212</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>431133; 512593</t>
+          <t>432130; 512662</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>573255; 671909</t>
+          <t>575757; 672395</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>797553; 915117</t>
+          <t>800775; 916990</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>855408; 969735</t>
+          <t>857136; 970154</t>
         </is>
       </c>
     </row>
